--- a/data/gravel/Orbea Terra 2025.xlsx
+++ b/data/gravel/Orbea Terra 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D971C0B1-2BF1-8C49-B579-7F3E180DAE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA54190-ADB2-0747-9A27-D2A6670E7FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{AE0F04AA-80E5-8247-9791-D6B95FAD9AB5}"/>
+    <workbookView xWindow="0" yWindow="860" windowWidth="28420" windowHeight="13680" xr2:uid="{AE0F04AA-80E5-8247-9791-D6B95FAD9AB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Orbea Terra 2025" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -68,12 +68,6 @@
     <t>carbon</t>
   </si>
   <si>
-    <t>frame weight</t>
-  </si>
-  <si>
-    <t>UDH</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -242,14 +236,128 @@
     <t>rider_max</t>
   </si>
   <si>
-    <t>a10:h33</t>
+    <t>udh</t>
+  </si>
+  <si>
+    <t>dropout</t>
+  </si>
+  <si>
+    <t>650B tire max</t>
+  </si>
+  <si>
+    <t>suspension corrected</t>
+  </si>
+  <si>
+    <t>rear axle</t>
+  </si>
+  <si>
+    <t>front axle</t>
+  </si>
+  <si>
+    <t>q-factor</t>
+  </si>
+  <si>
+    <t>seatpost diameter</t>
+  </si>
+  <si>
+    <t>routing shifter</t>
+  </si>
+  <si>
+    <t>routing dropper</t>
+  </si>
+  <si>
+    <t>routing dynamo</t>
+  </si>
+  <si>
+    <t>front derailleur</t>
+  </si>
+  <si>
+    <t>chainring 1</t>
+  </si>
+  <si>
+    <t>chainring 2</t>
+  </si>
+  <si>
+    <t>bottom bracket</t>
+  </si>
+  <si>
+    <t>mounts inner</t>
+  </si>
+  <si>
+    <t>mounts under</t>
+  </si>
+  <si>
+    <t>mounts top</t>
+  </si>
+  <si>
+    <t>mounts fork</t>
+  </si>
+  <si>
+    <t>mounts fender rear</t>
+  </si>
+  <si>
+    <t>mounts fender front</t>
+  </si>
+  <si>
+    <t>mounts rack</t>
+  </si>
+  <si>
+    <t>rotor max front</t>
+  </si>
+  <si>
+    <t>rotor max rear</t>
+  </si>
+  <si>
+    <t>frameset</t>
+  </si>
+  <si>
+    <t>base build</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>internal storage</t>
+  </si>
+  <si>
+    <t>frame_weight</t>
+  </si>
+  <si>
+    <t>BB386EVO</t>
+  </si>
+  <si>
+    <t>53/36</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>us</t>
+  </si>
+  <si>
+    <t>fork suspension</t>
+  </si>
+  <si>
+    <t>stem suspension</t>
+  </si>
+  <si>
+    <t>rear suspension</t>
+  </si>
+  <si>
+    <t>a10:h34</t>
+  </si>
+  <si>
+    <t>700c width max</t>
+  </si>
+  <si>
+    <t>ISO ASTM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -261,6 +369,12 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Futura Medium"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Futura"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -283,10 +397,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -621,18 +739,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{299AF885-3999-4E4F-8F92-5857EF0F7F08}">
-  <dimension ref="A1:Y35"/>
+  <dimension ref="A1:AH36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.83203125" style="1" customWidth="1"/>
-    <col min="3" max="8" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="10.83203125" style="1"/>
+    <col min="3" max="5" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" style="1" customWidth="1"/>
+    <col min="7" max="9" width="16.5" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" style="1"/>
     <col min="11" max="25" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -640,7 +760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -648,7 +768,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -656,7 +776,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -664,7 +784,7 @@
         <v>45853</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -672,107 +792,270 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:34" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AB6" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AD6" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AE6" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF6" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="AH6" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J7" s="1">
+        <v>142</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+      <c r="M7" s="1">
+        <v>27.2</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R7" s="1">
+        <v>50</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="U7" s="1">
+        <v>2</v>
+      </c>
+      <c r="V7" s="1">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>160</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>160</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>2999</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="O9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="P9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="Q9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="P9" s="1" t="s">
+      <c r="R9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Q9" s="1" t="s">
+      <c r="S9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="R9" s="1" t="s">
+      <c r="T9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="U9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="T9" s="1" t="s">
+      <c r="V9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="U9" s="1" t="s">
+      <c r="W9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="V9" s="1" t="s">
+      <c r="X9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="W9" s="1" t="s">
+      <c r="Y9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X9" s="1" t="s">
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="Y9" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="J10" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K10" s="1">
         <v>410</v>
@@ -820,12 +1103,12 @@
         <v>82.7</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>410</v>
@@ -846,7 +1129,7 @@
         <v>575</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K11" s="1">
         <v>440</v>
@@ -894,12 +1177,12 @@
         <v>79.5</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" s="1">
         <v>535</v>
@@ -920,7 +1203,7 @@
         <v>596</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K12" s="1">
         <v>470</v>
@@ -968,12 +1251,12 @@
         <v>76.2</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C13" s="1">
         <v>110</v>
@@ -994,7 +1277,7 @@
         <v>218</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K13" s="1">
         <v>505</v>
@@ -1042,12 +1325,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C14" s="1">
         <v>430</v>
@@ -1068,7 +1351,7 @@
         <v>430</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K14" s="1">
         <v>540</v>
@@ -1116,12 +1399,12 @@
         <v>71.400000000000006</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C15" s="1">
         <v>80</v>
@@ -1142,7 +1425,7 @@
         <v>80</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K15" s="1">
         <v>575</v>
@@ -1190,12 +1473,12 @@
         <v>69.8</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C16" s="1">
         <v>261</v>
@@ -1218,10 +1501,10 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C17" s="1">
         <v>1031</v>
@@ -1242,15 +1525,15 @@
         <v>1081</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C18" s="1">
         <v>69</v>
@@ -1271,15 +1554,15 @@
         <v>71</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C19" s="1">
         <v>74</v>
@@ -1300,15 +1583,15 @@
         <v>74</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20" s="1">
         <v>45</v>
@@ -1329,15 +1612,15 @@
         <v>45</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" s="1">
         <v>690</v>
@@ -1358,15 +1641,15 @@
         <v>828</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C22" s="1">
         <v>386</v>
@@ -1387,15 +1670,15 @@
         <v>417</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C23" s="1">
         <v>535</v>
@@ -1416,15 +1699,15 @@
         <v>645</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C24" s="1">
         <v>395</v>
@@ -1445,15 +1728,15 @@
         <v>395</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C25" s="1">
         <v>82.7</v>
@@ -1474,20 +1757,20 @@
         <v>69.8</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C27" s="1">
         <v>70</v>
@@ -1508,190 +1791,198 @@
         <v>110</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" s="1">
-        <v>700</v>
-      </c>
-      <c r="D29" s="1">
-        <v>700</v>
+        <v>94</v>
       </c>
       <c r="E29" s="1">
-        <v>700</v>
-      </c>
-      <c r="F29" s="1">
-        <v>700</v>
-      </c>
-      <c r="G29" s="1">
-        <v>700</v>
-      </c>
-      <c r="H29" s="1">
-        <v>700</v>
+        <v>1040</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C30" s="1">
-        <v>45</v>
+        <v>700</v>
       </c>
       <c r="D30" s="1">
-        <v>45</v>
+        <v>700</v>
       </c>
       <c r="E30" s="1">
-        <v>45</v>
+        <v>700</v>
       </c>
       <c r="F30" s="1">
-        <v>45</v>
+        <v>700</v>
       </c>
       <c r="G30" s="1">
-        <v>45</v>
+        <v>700</v>
       </c>
       <c r="H30" s="1">
-        <v>45</v>
+        <v>700</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C31" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D31" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E31" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F31" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G31" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H31" s="1">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C32" s="1">
-        <f>C34</f>
+        <v>50</v>
+      </c>
+      <c r="D32" s="1">
+        <v>50</v>
+      </c>
+      <c r="E32" s="1">
+        <v>50</v>
+      </c>
+      <c r="F32" s="1">
+        <v>50</v>
+      </c>
+      <c r="G32" s="1">
+        <v>50</v>
+      </c>
+      <c r="H32" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="1">
+        <f>C35</f>
         <v>155</v>
       </c>
-      <c r="D32" s="1">
-        <f>AVERAGE(D34,C35)</f>
+      <c r="D33" s="1">
+        <f>AVERAGE(D35,C36)</f>
         <v>166.5</v>
       </c>
-      <c r="E32" s="1">
-        <f t="shared" ref="E32:H32" si="0">AVERAGE(E34,D35)</f>
+      <c r="E33" s="1">
+        <f t="shared" ref="E33:H33" si="0">AVERAGE(E35,D36)</f>
         <v>172.5</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F33" s="1">
         <f t="shared" si="0"/>
         <v>179.5</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G33" s="1">
         <f t="shared" si="0"/>
         <v>185.5</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H33" s="1">
         <f t="shared" si="0"/>
         <v>191.5</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="1">
-        <f>D32</f>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="1">
+        <f>D33</f>
         <v>166.5</v>
       </c>
-      <c r="D33" s="1">
-        <f t="shared" ref="D33:G33" si="1">E32</f>
+      <c r="D34" s="1">
+        <f t="shared" ref="D34:G34" si="1">E33</f>
         <v>172.5</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E34" s="1">
         <f t="shared" si="1"/>
         <v>179.5</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F34" s="1">
         <f t="shared" si="1"/>
         <v>185.5</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G34" s="1">
         <f t="shared" si="1"/>
         <v>191.5</v>
       </c>
-      <c r="H33" s="1">
-        <f t="shared" ref="H33" si="2">H35</f>
+      <c r="H34" s="1">
+        <f t="shared" ref="H34" si="2">H36</f>
         <v>207</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C34" s="1">
-        <v>155</v>
-      </c>
-      <c r="D34" s="1">
-        <v>167</v>
-      </c>
-      <c r="E34" s="1">
-        <v>173</v>
-      </c>
-      <c r="F34" s="1">
-        <v>180</v>
-      </c>
-      <c r="G34" s="1">
-        <v>186</v>
-      </c>
-      <c r="H34" s="1">
-        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C35" s="1">
+        <v>155</v>
+      </c>
+      <c r="D35" s="1">
+        <v>167</v>
+      </c>
+      <c r="E35" s="1">
+        <v>173</v>
+      </c>
+      <c r="F35" s="1">
+        <v>180</v>
+      </c>
+      <c r="G35" s="1">
+        <v>186</v>
+      </c>
+      <c r="H35" s="1">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C36" s="1">
         <v>166</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D36" s="1">
         <v>172</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E36" s="1">
         <v>179</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F36" s="1">
         <v>185</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G36" s="1">
         <v>191</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H36" s="1">
         <v>207</v>
       </c>
     </row>

--- a/data/gravel/Orbea Terra 2025.xlsx
+++ b/data/gravel/Orbea Terra 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4CD2BF-F948-B944-ABE7-9AA095A10027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA6D7F6-BF48-B845-8B98-97DA0F0097AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="13120" windowHeight="6100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="19040" windowHeight="15200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -262,9 +262,6 @@
     <t>bottom_bracket</t>
   </si>
   <si>
-    <t>pf</t>
-  </si>
-  <si>
     <t>q_factor</t>
   </si>
   <si>
@@ -349,9 +346,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -368,17 +362,29 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>press fit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Futura"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -401,8 +407,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1335,26 +1342,26 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B36" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B37" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1398,33 +1405,21 @@
       <c r="A43" t="s">
         <v>70</v>
       </c>
-      <c r="B43" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>72</v>
       </c>
-      <c r="B44" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>73</v>
       </c>
-      <c r="B45" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>74</v>
       </c>
-      <c r="B46" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
@@ -1446,26 +1441,26 @@
       <c r="A49" t="s">
         <v>79</v>
       </c>
-      <c r="B49" t="s">
-        <v>80</v>
+      <c r="B49" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>81</v>
+      </c>
+      <c r="B51" t="s">
         <v>82</v>
-      </c>
-      <c r="B51" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B52" t="s">
         <v>64</v>
@@ -1473,7 +1468,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B53" t="s">
         <v>68</v>
@@ -1481,51 +1476,51 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>85</v>
+      </c>
+      <c r="B54" t="s">
         <v>86</v>
-      </c>
-      <c r="B54" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>87</v>
+      </c>
+      <c r="B55" t="s">
         <v>88</v>
-      </c>
-      <c r="B55" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B56" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B61" t="s">
         <v>64</v>
@@ -1533,15 +1528,15 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>95</v>
+      </c>
+      <c r="B62" t="s">
         <v>96</v>
-      </c>
-      <c r="B62" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B63" t="s">
         <v>66</v>
@@ -1549,12 +1544,12 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B65" t="s">
         <v>64</v>
@@ -1562,7 +1557,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B66" t="s">
         <v>64</v>
@@ -1570,12 +1565,12 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B68" t="s">
         <v>71</v>
@@ -1583,28 +1578,28 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>104</v>
+      </c>
+      <c r="B70" t="s">
         <v>105</v>
-      </c>
-      <c r="B70" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>108</v>
-      </c>
-      <c r="B72" t="s">
-        <v>109</v>
+        <v>107</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Orbea Terra 2025.xlsx
+++ b/data/gravel/Orbea Terra 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA6D7F6-BF48-B845-8B98-97DA0F0097AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6A9E1C-4E20-C04F-BC95-628E36A6F2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="19040" windowHeight="15200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41980" yWindow="-15960" windowWidth="19040" windowHeight="15200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>press fit</t>
+  </si>
+  <si>
+    <t>https://orbea.eus/microsite/terra/assets/img/terra-highlights.webp</t>
   </si>
 </sst>
 </file>
@@ -752,6 +755,11 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>116</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>

--- a/data/gravel/Orbea Terra 2025.xlsx
+++ b/data/gravel/Orbea Terra 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6A9E1C-4E20-C04F-BC95-628E36A6F2B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2667F82-E19F-E245-BC9F-ECE3A06ABAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41980" yWindow="-15960" windowWidth="19040" windowHeight="15200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8280" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -280,9 +280,6 @@
     <t>max_chainring_2x</t>
   </si>
   <si>
-    <t>53/36</t>
-  </si>
-  <si>
     <t>rotor_max_front</t>
   </si>
   <si>
@@ -371,6 +368,12 @@
   </si>
   <si>
     <t>https://orbea.eus/microsite/terra/assets/img/terra-highlights.webp</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Mallabia, Spain</t>
   </si>
 </sst>
 </file>
@@ -709,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -757,7 +760,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1350,26 +1353,26 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" t="s">
         <v>108</v>
-      </c>
-      <c r="B35" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>109</v>
+      </c>
+      <c r="B36" t="s">
         <v>110</v>
-      </c>
-      <c r="B36" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" t="s">
         <v>112</v>
-      </c>
-      <c r="B37" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1450,7 +1453,7 @@
         <v>79</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -1486,49 +1489,49 @@
       <c r="A54" t="s">
         <v>85</v>
       </c>
-      <c r="B54" t="s">
-        <v>86</v>
+      <c r="B54">
+        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>86</v>
+      </c>
+      <c r="B55" t="s">
         <v>87</v>
-      </c>
-      <c r="B55" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B56" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B61" t="s">
         <v>64</v>
@@ -1536,28 +1539,25 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>94</v>
+      </c>
+      <c r="B62" t="s">
         <v>95</v>
-      </c>
-      <c r="B62" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>97</v>
-      </c>
-      <c r="B63" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B65" t="s">
         <v>64</v>
@@ -1565,7 +1565,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B66" t="s">
         <v>64</v>
@@ -1573,12 +1573,12 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B68" t="s">
         <v>71</v>
@@ -1586,28 +1586,36 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>103</v>
+      </c>
+      <c r="B70" t="s">
         <v>104</v>
-      </c>
-      <c r="B70" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>116</v>
+      </c>
+      <c r="B73" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Orbea Terra 2025.xlsx
+++ b/data/gravel/Orbea Terra 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2667F82-E19F-E245-BC9F-ECE3A06ABAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131DB6F3-292B-B341-8FB4-6837859613A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8280" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t>Mallabia, Spain</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -1523,6 +1526,9 @@
       <c r="A59" t="s">
         <v>91</v>
       </c>
+      <c r="B59" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">

--- a/data/gravel/Orbea Terra 2025.xlsx
+++ b/data/gravel/Orbea Terra 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131DB6F3-292B-B341-8FB4-6837859613A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8638E77-6561-794B-AE9D-3B4A19D5AC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -377,6 +377,24 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -715,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1453,174 +1471,204 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>79</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>81</v>
-      </c>
-      <c r="B51" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>83</v>
-      </c>
-      <c r="B52" t="s">
-        <v>64</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>84</v>
-      </c>
-      <c r="B53" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>85</v>
-      </c>
-      <c r="B54">
-        <v>53</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>86</v>
-      </c>
-      <c r="B55" t="s">
-        <v>87</v>
+        <v>79</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>88</v>
-      </c>
-      <c r="B56" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>89</v>
+        <v>81</v>
+      </c>
+      <c r="B57" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>90</v>
+        <v>83</v>
+      </c>
+      <c r="B58" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B59" t="s">
-        <v>118</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>92</v>
+        <v>85</v>
+      </c>
+      <c r="B60">
+        <v>53</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B61" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B62" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>99</v>
-      </c>
-      <c r="B66" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>100</v>
+        <v>93</v>
+      </c>
+      <c r="B67" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>103</v>
-      </c>
-      <c r="B70" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>105</v>
+        <v>98</v>
+      </c>
+      <c r="B71" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>106</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>113</v>
+        <v>99</v>
+      </c>
+      <c r="B72" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>101</v>
+      </c>
+      <c r="B74" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>103</v>
+      </c>
+      <c r="B76" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>106</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>116</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>117</v>
       </c>
     </row>
